--- a/data/demand.xlsx
+++ b/data/demand.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>day</t>
   </si>
@@ -98,6 +98,9 @@
   </si>
   <si>
     <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
@@ -698,6 +701,86 @@
         <v>18</v>
       </c>
     </row>
+    <row r="4" spans="1:26">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>11</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>11</v>
+      </c>
+      <c r="L4">
+        <v>12</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>11</v>
+      </c>
+      <c r="O4">
+        <v>13</v>
+      </c>
+      <c r="P4">
+        <v>16</v>
+      </c>
+      <c r="Q4">
+        <v>18</v>
+      </c>
+      <c r="R4">
+        <v>17</v>
+      </c>
+      <c r="S4">
+        <v>16</v>
+      </c>
+      <c r="T4">
+        <v>15</v>
+      </c>
+      <c r="U4">
+        <v>16</v>
+      </c>
+      <c r="V4">
+        <v>14</v>
+      </c>
+      <c r="W4">
+        <v>11</v>
+      </c>
+      <c r="X4">
+        <v>7</v>
+      </c>
+      <c r="Y4">
+        <v>5</v>
+      </c>
+      <c r="Z4">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
